--- a/biljart moyenne.xlsx
+++ b/biljart moyenne.xlsx
@@ -3,9 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{892A891E-0351-5740-95FE-A5F2641F589F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\MyTech\Github\biljart\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{347DEFAE-23CD-4B44-A31D-6D52782D1FEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1320" yWindow="480" windowWidth="9960" windowHeight="15465" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -77,7 +82,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
@@ -395,7 +400,7 @@
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.14453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.87109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="5" width="11.97265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
